--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_miginterna_a_2020_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_miginterna_a_2020_magallanes.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:15</t>
+    <t xml:space="preserve">2026-09-24 01:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -656,19 +656,19 @@
         <v>14</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>-0.56</v>
+        <v>-0.26</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>-0.44</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="8">
@@ -679,19 +679,19 @@
         <v>14</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.13</v>
+        <v>0.44</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.07</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="9">
@@ -702,19 +702,19 @@
         <v>14</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.02</v>
+        <v>0.37</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-0.04</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="10">
@@ -770,17 +770,21 @@
       <c r="B12" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="2"/>
+      <c r="C12" s="2" t="n">
+        <v>-0.93</v>
+      </c>
       <c r="D12" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>336</v>
-      </c>
-      <c r="G12" s="2"/>
+        <v>337</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>-0.93</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
@@ -789,17 +793,21 @@
       <c r="B13" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="2"/>
+      <c r="C13" s="2" t="n">
+        <v>-0.93</v>
+      </c>
       <c r="D13" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>0.04</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>336</v>
-      </c>
-      <c r="G13" s="2"/>
+        <v>337</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>-0.97</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
@@ -855,19 +863,19 @@
         <v>14</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0.22</v>
+        <v>0.46</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.12</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.37</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="17">
@@ -878,19 +886,19 @@
         <v>14</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>-0.2</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="18">
@@ -920,19 +928,19 @@
         <v>28</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0.33</v>
+        <v>0.11</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="20">
@@ -943,19 +951,19 @@
         <v>28</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.3</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.07</v>
+        <v>0.04</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>-0.31</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="21">
@@ -966,19 +974,19 @@
         <v>28</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.23</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="22">
@@ -989,19 +997,19 @@
         <v>28</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>0.23</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="23">
@@ -1012,19 +1020,19 @@
         <v>28</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>-0.55</v>
+        <v>-0.43</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.31</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="24">
@@ -1035,19 +1043,19 @@
         <v>28</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.15</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_miginterna_a_2020_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_miginterna_a_2020_magallanes.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:05</t>
+    <t xml:space="preserve">2026-10-01 23:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_miginterna_a_2020_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_miginterna_a_2020_magallanes.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:15</t>
+    <t xml:space="preserve">2026-10-05 19:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
